--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486423_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486423_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2872</v>
+        <v>6.1572</v>
       </c>
       <c r="E2" t="n">
-        <v>4.62</v>
+        <v>3.4592</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6672</v>
+        <v>2.698</v>
       </c>
       <c r="G2" t="n">
         <v>5.7132</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1836</v>
+        <v>1.0536</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5057</v>
+        <v>0.3449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1745</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3153</v>
+        <v>3.2219</v>
       </c>
       <c r="E3" t="n">
-        <v>1.314</v>
+        <v>1.1589</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0013</v>
+        <v>2.063</v>
       </c>
       <c r="G3" t="n">
         <v>0.5911999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4641</v>
+        <v>0.3707</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0721</v>
+        <v>-0.0829</v>
       </c>
       <c r="U3" t="n">
-        <v>0.392</v>
+        <v>0.4536</v>
       </c>
       <c r="V3" t="n">
         <v>2.2599</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6429</v>
+        <v>2.4331</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.194</v>
+        <v>-0.2805</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8369</v>
+        <v>2.7136</v>
       </c>
       <c r="G4" t="n">
         <v>0.4187</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8767</v>
+        <v>0.6669</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3389</v>
+        <v>-0.4254</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2156</v>
+        <v>1.0923</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0688</v>
+        <v>2.0747</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7711</v>
+        <v>1.6846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2977</v>
+        <v>0.3901</v>
       </c>
       <c r="G5" t="n">
         <v>1.0484</v>
@@ -844,13 +844,13 @@
         <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3032</v>
+        <v>0.3091</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0649</v>
+        <v>-0.1514</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3681</v>
+        <v>0.4605</v>
       </c>
       <c r="V5" t="n">
         <v>0.9347</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9745</v>
+        <v>1.4468</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0833</v>
+        <v>-0.611</v>
       </c>
       <c r="F6" t="n">
         <v>2.0578</v>
@@ -922,10 +922,10 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0601</v>
+        <v>0.4122</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0154</v>
+        <v>-0.5432</v>
       </c>
       <c r="U6" t="n">
         <v>0.9553</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4937</v>
+        <v>1.201</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.897</v>
+        <v>-0.313</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3907</v>
+        <v>1.514</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5373</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2963</v>
+        <v>0.411</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6044</v>
+        <v>-0.0204</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3081</v>
+        <v>0.4314</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0479</v>
+        <v>-0.0171</v>
       </c>
       <c r="E8" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0479</v>
+        <v>-0.0171</v>
       </c>
       <c r="T8" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9419</v>
+        <v>-0.4341</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.522</v>
+        <v>-0.23</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4199</v>
+        <v>-0.2041</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5583</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4282</v>
+        <v>0.0796</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.536</v>
+        <v>-0.2439</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1078</v>
+        <v>0.3235</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3904</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4574</v>
+        <v>-1.9774</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6594</v>
+        <v>-4.9636</v>
       </c>
       <c r="F10" t="n">
-        <v>3.202</v>
+        <v>2.9863</v>
       </c>
       <c r="G10" t="n">
         <v>1.6515</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.481</v>
+        <v>0.961</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9349</v>
+        <v>-0.2391</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4159</v>
+        <v>1.2002</v>
       </c>
       <c r="V10" t="n">
         <v>0.1952</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6315</v>
+        <v>-2.2834</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9313</v>
+        <v>-3.4915</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7000999999999999</v>
+        <v>1.2081</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5578</v>
+        <v>-1.7681</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.596</v>
+        <v>-1.9736</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0382</v>
+        <v>0.2056</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7068</v>
+        <v>-1.6628</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7451</v>
+        <v>-1.7393</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0382</v>
+        <v>0.0765</v>
       </c>
       <c r="M11" t="n">
-        <v>0.149</v>
+        <v>-0.1053</v>
       </c>
       <c r="N11" t="n">
-        <v>0.149</v>
+        <v>-0.2344</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.1291</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1438</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.137</v>
+        <v>-0.3497</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2808</v>
+        <v>0.4434</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.13</v>
+        <v>-1.479</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-1.479</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6323</v>
+        <v>-2.7239</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9638</v>
+        <v>-1.9313</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3314</v>
+        <v>-0.7926</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7681</v>
+        <v>-0.5578</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9736</v>
+        <v>-0.596</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2056</v>
+        <v>0.0382</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6628</v>
+        <v>-0.7068</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7393</v>
+        <v>-0.7451</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0765</v>
+        <v>0.0382</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1053</v>
+        <v>0.149</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2344</v>
+        <v>0.149</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1291</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2552</v>
+        <v>0.0514</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.822</v>
+        <v>-0.137</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5667</v>
+        <v>0.1884</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.479</v>
+        <v>-1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.479</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.071400000000001</v>
+        <v>9.098800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.6142</v>
+        <v>-5.5867</v>
       </c>
       <c r="F13" t="n">
-        <v>14.6855</v>
+        <v>14.6856</v>
       </c>
       <c r="G13" t="n">
         <v>6.343299999999999</v>
@@ -1441,7 +1441,7 @@
         <v>-2.8568</v>
       </c>
       <c r="J13" t="n">
-        <v>6.714899999999999</v>
+        <v>6.714899999999998</v>
       </c>
       <c r="K13" t="n">
         <v>5.248399999999999</v>
@@ -1450,7 +1450,7 @@
         <v>1.4664</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3717</v>
+        <v>-0.3716999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>3.9515</v>
@@ -1459,7 +1459,7 @@
         <v>-4.323099999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.4378</v>
+        <v>-5.437799999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.3129</v>
@@ -1468,10 +1468,10 @@
         <v>10.8752</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3647</v>
+        <v>4.3921</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9442</v>
+        <v>-1.9166</v>
       </c>
       <c r="U13" t="n">
         <v>6.3087</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2577</v>
+        <v>3.692</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2302</v>
+        <v>2.3739</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0274</v>
+        <v>1.3181</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0949</v>
+        <v>3.9346</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5138</v>
+        <v>-0.8242</v>
       </c>
       <c r="I14" t="n">
-        <v>2.581</v>
+        <v>4.7589</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5317</v>
+        <v>4.5093</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9307</v>
+        <v>-0.5229</v>
       </c>
       <c r="L14" t="n">
-        <v>2.601</v>
+        <v>5.0322</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4368</v>
+        <v>-0.5747</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4169</v>
+        <v>-0.3013</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0199</v>
+        <v>-0.2733</v>
       </c>
       <c r="P14" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9576</v>
+        <v>2.8276</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3168</v>
+        <v>-0.5137</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2139</v>
+        <v>-1.0479</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1029</v>
+        <v>0.5341</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3904</v>
+        <v>-1.469</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3904</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.762</v>
+        <v>3.2692</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9269</v>
+        <v>2.1185</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8351</v>
+        <v>1.1507</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9346</v>
+        <v>3.0949</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8242</v>
+        <v>0.5138</v>
       </c>
       <c r="I15" t="n">
-        <v>4.7589</v>
+        <v>2.581</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5093</v>
+        <v>3.5317</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5229</v>
+        <v>0.9307</v>
       </c>
       <c r="L15" t="n">
-        <v>5.0322</v>
+        <v>2.601</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5747</v>
+        <v>-0.4368</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3013</v>
+        <v>-0.4169</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2733</v>
+        <v>-0.0199</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8276</v>
+        <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4437</v>
+        <v>-0.3052</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4949</v>
+        <v>-0.3256</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0512</v>
+        <v>0.0204</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.469</v>
+        <v>-0.3904</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.469</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0105</v>
+        <v>-0.1771</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9301</v>
+        <v>-1.6006</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9406</v>
+        <v>1.4235</v>
       </c>
       <c r="G16" t="n">
         <v>-0.144</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2759</v>
+        <v>0.0883</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0733</v>
+        <v>-0.7438</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3492</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-0.339</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0348</v>
+        <v>-1.0074</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6962</v>
+        <v>-1.4551</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6613</v>
+        <v>0.4478</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6038</v>
+        <v>-0.1543</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8492</v>
+        <v>-0.3375</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2454</v>
+        <v>0.1833</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9</v>
+        <v>-0.0179</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3989</v>
+        <v>0.4594</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4989</v>
+        <v>-0.4773</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7038</v>
+        <v>-0.1364</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4504</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2534</v>
+        <v>0.6606</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2862</v>
+        <v>0.0493</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5312</v>
+        <v>-0.3497</v>
       </c>
       <c r="U17" t="n">
-        <v>0.755</v>
+        <v>0.399</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3698</v>
+        <v>-1.1199</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-1.1199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.33</v>
+        <v>-1.0804</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.674</v>
+        <v>-1.3667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.344</v>
+        <v>0.2863</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6928</v>
+        <v>-1.6038</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1796</v>
+        <v>-1.8492</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5132</v>
+        <v>0.2454</v>
       </c>
       <c r="J18" t="n">
-        <v>0.093</v>
+        <v>-0.9</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0547</v>
+        <v>-1.3989</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>0.4989</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.7038</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2344</v>
+        <v>-0.4504</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5514</v>
+        <v>-0.2534</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5926</v>
+        <v>0.2406</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0601</v>
+        <v>-0.1394</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5325</v>
+        <v>0.38</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3597</v>
+        <v>-0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7395</v>
+        <v>0.7602</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3798</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3935</v>
+        <v>-1.4409</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.134</v>
+        <v>-4.0223</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7406</v>
+        <v>2.5813</v>
       </c>
       <c r="G19" t="n">
         <v>-2.529</v>
@@ -1936,13 +1936,13 @@
         <v>3.0451</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.125</v>
+        <v>-0.1724</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9553</v>
+        <v>-0.8436</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8304</v>
+        <v>0.6711</v>
       </c>
       <c r="V19" t="n">
         <v>0.3904</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7382</v>
+        <v>-1.7936</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7904</v>
+        <v>-2.0092</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0522</v>
+        <v>0.2156</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1543</v>
+        <v>-0.6928</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3375</v>
+        <v>-0.1796</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1833</v>
+        <v>-0.5132</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0179</v>
+        <v>0.093</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4594</v>
+        <v>0.0547</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4773</v>
+        <v>0.0382</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1364</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.2344</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6606</v>
+        <v>-0.5514</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6816</v>
+        <v>0.1289</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2752</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0034</v>
+        <v>0.4041</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1199</v>
+        <v>-0.3597</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1199</v>
+        <v>0.3798</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2851</v>
+        <v>-2.1669</v>
       </c>
       <c r="E21" t="n">
         <v>-1.9384</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3467</v>
+        <v>-0.2285</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6449</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7055</v>
+        <v>-0.5873</v>
       </c>
       <c r="T21" t="n">
         <v>-0.8868</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1813</v>
+        <v>0.2995</v>
       </c>
       <c r="V21" t="n">
         <v>0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0689</v>
+        <v>-2.3752</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0369</v>
+        <v>-2.5899</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0319</v>
+        <v>0.2147</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6288</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0926</v>
+        <v>-0.399</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0274</v>
+        <v>-0.5804</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.06510000000000001</v>
+        <v>0.1815</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.251</v>
+        <v>-3.5008</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6427</v>
+        <v>-4.1957</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3918</v>
+        <v>0.6949</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9753</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1542</v>
+        <v>-0.4041</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5634</v>
+        <v>-1.1164</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4092</v>
+        <v>0.7123</v>
       </c>
       <c r="V23" t="n">
         <v>-0.339</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.071300000000001</v>
+        <v>-6.581099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.6856</v>
+        <v>-14.6855</v>
       </c>
       <c r="F24" t="n">
-        <v>6.6144</v>
+        <v>8.1044</v>
       </c>
       <c r="G24" t="n">
         <v>-6.343399999999999</v>
@@ -2296,10 +2296,10 @@
         <v>-9.200099999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>2.856800000000001</v>
+        <v>2.8568</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3718000000000008</v>
+        <v>0.3717999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>-3.9516</v>
@@ -2326,13 +2326,13 @@
         <v>16.313</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.3647</v>
+        <v>-1.8746</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.3087</v>
+        <v>-6.3088</v>
       </c>
       <c r="U24" t="n">
-        <v>2.9442</v>
+        <v>4.4342</v>
       </c>
       <c r="V24" t="n">
         <v>-3.8012</v>
@@ -2341,7 +2341,7 @@
         <v>2.1268</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.9279</v>
+        <v>-5.927899999999999</v>
       </c>
     </row>
   </sheetData>
